--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484670_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484670_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4711</v>
+        <v>10.0919</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7112</v>
+        <v>8.3817</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7598</v>
+        <v>1.7103</v>
       </c>
       <c r="G2" t="n">
         <v>5.737</v>
@@ -610,13 +610,13 @@
         <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7369</v>
+        <v>0.3578</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9503</v>
+        <v>0.6207</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2133</v>
+        <v>-0.2629</v>
       </c>
       <c r="V2" t="n">
         <v>6.0129</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5177</v>
+        <v>3.3834</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4418</v>
+        <v>1.2084</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0759</v>
+        <v>2.175</v>
       </c>
       <c r="G3" t="n">
         <v>1.913</v>
@@ -688,13 +688,13 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4318</v>
+        <v>0.2975</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7119</v>
+        <v>0.4785</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2801</v>
+        <v>-0.181</v>
       </c>
       <c r="V3" t="n">
         <v>0.6231</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4841</v>
+        <v>2.2702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4311</v>
+        <v>1.1181</v>
       </c>
       <c r="F4" t="n">
-        <v>1.053</v>
+        <v>1.1521</v>
       </c>
       <c r="G4" t="n">
         <v>1.7971</v>
@@ -766,13 +766,13 @@
         <v>2.0158</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.363</v>
+        <v>-0.5769</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9359</v>
+        <v>-0.2489</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4272</v>
+        <v>-0.3281</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9658</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CASADO SEGURA</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4382</v>
+        <v>2.2379</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6801</v>
+        <v>4.5216</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7581</v>
+        <v>-2.2837</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5411</v>
+        <v>1.1155</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2942</v>
+        <v>1.2949</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2469</v>
+        <v>-0.1794</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6019</v>
+        <v>3.155</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1116</v>
+        <v>2.4367</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4902</v>
+        <v>0.7183</v>
       </c>
       <c r="M5" t="n">
-        <v>1.143</v>
+        <v>-2.0395</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4059</v>
+        <v>-1.1418</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7371</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8971</v>
+        <v>0.0228</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1592</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.262</v>
+        <v>-0.0767</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5889</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3334</v>
+        <v>0.4166</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8896</v>
+        <v>0.5374</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5562</v>
+        <v>-0.1208</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1155</v>
+        <v>0.0333</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2949</v>
+        <v>-0.7748</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1794</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.155</v>
+        <v>0.5891</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4367</v>
+        <v>-0.155</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7183</v>
+        <v>0.7441</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0395</v>
+        <v>-0.5558</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1418</v>
+        <v>-0.6198</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8977000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8817</v>
+        <v>-0.0277</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5324</v>
+        <v>-0.0516</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3493</v>
+        <v>0.0239</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>J. CASADO SEGURA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1708</v>
+        <v>0.1501</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6703</v>
+        <v>-0.7071</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8411</v>
+        <v>0.8572</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3192</v>
+        <v>0.5411</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0397</v>
+        <v>0.2942</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3589</v>
+        <v>0.2469</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6153</v>
+        <v>-0.6019</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.1116</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6153</v>
+        <v>-0.4902</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2961</v>
+        <v>1.143</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0397</v>
+        <v>0.4059</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2564</v>
+        <v>0.7371</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3665</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3665</v>
+        <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1234</v>
+        <v>0.609</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0551</v>
+        <v>0.7719</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1785</v>
+        <v>-0.1629</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.102</v>
+        <v>0.1486</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2364</v>
+        <v>-0.5191</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1343</v>
+        <v>0.6677</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4389</v>
+        <v>-0.3192</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4137</v>
+        <v>0.0397</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8526</v>
+        <v>-0.3589</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4401</v>
+        <v>-0.6153</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5235</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0833</v>
+        <v>-0.6153</v>
       </c>
       <c r="M8" t="n">
-        <v>0.879</v>
+        <v>0.2961</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1098</v>
+        <v>0.0397</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7692</v>
+        <v>0.2564</v>
       </c>
       <c r="P8" t="n">
         <v>0.3665</v>
@@ -1078,28 +1078,28 @@
         <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>1.197</v>
+        <v>0.1012</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6765</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5206</v>
+        <v>0.0051</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.243</v>
+        <v>0.0701</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0016</v>
+        <v>0.0171</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2447</v>
+        <v>0.053</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0333</v>
+        <v>1.6416</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7748</v>
+        <v>-1.6376</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8080000000000001</v>
+        <v>3.2792</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5891</v>
+        <v>-0.5195</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.155</v>
+        <v>-2.0039</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7441</v>
+        <v>1.4844</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5558</v>
+        <v>2.1611</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6198</v>
+        <v>0.3662</v>
       </c>
       <c r="O9" t="n">
-        <v>0.064</v>
+        <v>1.7949</v>
       </c>
       <c r="P9" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6874</v>
+        <v>0.0462</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5875</v>
+        <v>0.1859</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0999</v>
+        <v>-0.1397</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>-2.5339</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>-3.8009</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2923</v>
+        <v>-0.22</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5187</v>
+        <v>0.2364</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2264</v>
+        <v>-0.4564</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6416</v>
+        <v>0.4389</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6376</v>
+        <v>-0.4137</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2792</v>
+        <v>0.8526</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5195</v>
+        <v>-0.4401</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.0039</v>
+        <v>-0.5235</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4844</v>
+        <v>0.0833</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1611</v>
+        <v>0.879</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3662</v>
+        <v>0.1098</v>
       </c>
       <c r="O10" t="n">
-        <v>1.7949</v>
+        <v>0.7692</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9163</v>
+        <v>0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3162</v>
+        <v>0.875</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3499</v>
+        <v>0.6765</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0337</v>
+        <v>0.1985</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.5339</v>
+        <v>-1.9005</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.8009</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.208</v>
+        <v>-2.2739</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.476</v>
+        <v>-0.5171</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7321</v>
+        <v>-1.7569</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1448</v>
@@ -1312,13 +1312,13 @@
         <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2037</v>
+        <v>0.1378</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3839</v>
+        <v>0.3428</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1802</v>
+        <v>-0.205</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9005</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5358</v>
+        <v>-2.6785</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6745</v>
+        <v>-1.8669</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8612</v>
+        <v>-0.8117</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7436</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3807</v>
+        <v>0.2379</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4208</v>
+        <v>0.2285</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0401</v>
+        <v>0.0094</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6231</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4669</v>
+        <v>-4.2746</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7982</v>
+        <v>-2.6059</v>
       </c>
       <c r="F13" t="n">
         <v>-1.6687</v>
@@ -1468,10 +1468,10 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1101</v>
+        <v>0.3024</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2021</v>
+        <v>-0.0098</v>
       </c>
       <c r="U13" t="n">
         <v>0.3122</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.771299999999997</v>
+        <v>9.3218</v>
       </c>
       <c r="E14" t="n">
-        <v>9.254100000000001</v>
+        <v>9.804600000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4829000000000003</v>
+        <v>-0.4829000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>8.9381</v>
@@ -1519,16 +1519,16 @@
         <v>5.9313</v>
       </c>
       <c r="J14" t="n">
-        <v>8.330299999999998</v>
+        <v>8.330300000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>6.884500000000002</v>
+        <v>6.8845</v>
       </c>
       <c r="L14" t="n">
         <v>1.4458</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6078999999999997</v>
+        <v>0.6079000000000006</v>
       </c>
       <c r="N14" t="n">
         <v>-3.878</v>
@@ -1546,16 +1546,16 @@
         <v>14.6606</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8324</v>
+        <v>2.383</v>
       </c>
       <c r="T14" t="n">
-        <v>2.639699999999999</v>
+        <v>3.1903</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8071000000000002</v>
+        <v>-0.8071999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.832100000000001</v>
+        <v>-3.8321</v>
       </c>
       <c r="W14" t="n">
         <v>11.112</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>13.6432</v>
+        <v>11.6182</v>
       </c>
       <c r="E15" t="n">
-        <v>14.1083</v>
+        <v>11.6083</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4651</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>2.7343</v>
@@ -1624,13 +1624,13 @@
         <v>1.6493</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9039</v>
+        <v>0.879</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5694</v>
+        <v>1.0694</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6655</v>
+        <v>-0.1904</v>
       </c>
       <c r="V15" t="n">
         <v>6.3557</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1862</v>
+        <v>1.5811</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4736</v>
+        <v>1.6569</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2874</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7321</v>
+        <v>1.1332</v>
       </c>
       <c r="H16" t="n">
-        <v>2.713</v>
+        <v>2.505</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0191</v>
+        <v>-1.3718</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1138</v>
+        <v>3.2859</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4213</v>
+        <v>3.8239</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6925</v>
+        <v>-0.538</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3818</v>
+        <v>-2.1526</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7083</v>
+        <v>-1.3189</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6735</v>
+        <v>-0.8338</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9163</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0158</v>
+        <v>-2.9321</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0039</v>
+        <v>-0.4813</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1086</v>
+        <v>-0.2858</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1047</v>
+        <v>-0.1955</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6335</v>
+        <v>2.212</v>
       </c>
       <c r="W16" t="n">
-        <v>1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.9005</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9456</v>
+        <v>1.329</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1785</v>
+        <v>3.6659</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1242</v>
+        <v>-2.3369</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2517</v>
+        <v>2.7321</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0367</v>
+        <v>2.713</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.215</v>
+        <v>0.0191</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.711</v>
+        <v>4.1138</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1116</v>
+        <v>3.4213</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5994</v>
+        <v>0.6925</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5407</v>
+        <v>-1.3818</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.925</v>
+        <v>-0.7083</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3843</v>
+        <v>-0.6735</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4661</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5357</v>
+        <v>0.1467</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7345</v>
+        <v>0.3009</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1988</v>
+        <v>-0.1542</v>
       </c>
       <c r="V17" t="n">
-        <v>1.267</v>
+        <v>-0.6335</v>
       </c>
       <c r="W17" t="n">
         <v>1.267</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4548</v>
+        <v>1.1335</v>
       </c>
       <c r="E18" t="n">
-        <v>1.08</v>
+        <v>0.3022</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6251</v>
+        <v>0.8312</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1332</v>
+        <v>-1.2517</v>
       </c>
       <c r="H18" t="n">
-        <v>2.505</v>
+        <v>-1.0367</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3718</v>
+        <v>-0.215</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2859</v>
+        <v>-0.711</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8239</v>
+        <v>-0.1116</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.538</v>
+        <v>-0.5994</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1526</v>
+        <v>-0.5407</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3189</v>
+        <v>-0.925</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8338</v>
+        <v>0.3843</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6076</v>
+        <v>-0.3479</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8627</v>
+        <v>-0.2537</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7449</v>
+        <v>-0.0941</v>
       </c>
       <c r="V18" t="n">
-        <v>2.212</v>
+        <v>1.267</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5889</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2294</v>
+        <v>-1.0328</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8352</v>
+        <v>-3.6429</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6058</v>
+        <v>2.6101</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4431</v>
@@ -1936,13 +1936,13 @@
         <v>2.0158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6135</v>
+        <v>-0.4169</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3506</v>
+        <v>-0.1583</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2629</v>
+        <v>-0.2585</v>
       </c>
       <c r="V19" t="n">
         <v>0.6439</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3729</v>
+        <v>-3.2884</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2816</v>
+        <v>-2.4739</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0913</v>
+        <v>-0.8144</v>
       </c>
       <c r="G20" t="n">
         <v>-4.7171</v>
@@ -2014,13 +2014,13 @@
         <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4884</v>
+        <v>-0.4038</v>
       </c>
       <c r="T20" t="n">
-        <v>0.089</v>
+        <v>-0.1033</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5774</v>
+        <v>-0.3005</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5517</v>
+        <v>-3.3653</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0917</v>
+        <v>-4.7071</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5399</v>
+        <v>1.3418</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2114</v>
@@ -2092,13 +2092,13 @@
         <v>0.5498</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0575</v>
+        <v>0.129</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.184</v>
+        <v>0.2006</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1265</v>
+        <v>-0.0717</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2831</v>
+        <v>-3.7994</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8258</v>
+        <v>-1.4412</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4573</v>
+        <v>-2.3582</v>
       </c>
       <c r="G22" t="n">
         <v>0.5726</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.0551</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0166</v>
+        <v>0.4012</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5554</v>
+        <v>-0.4563</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5681</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3961</v>
+        <v>-4.3029</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5151</v>
+        <v>-1.3228</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.881</v>
+        <v>-2.9801</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1107</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1754</v>
+        <v>-0.0822</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2753</v>
+        <v>-0.083</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0998</v>
+        <v>0.0007</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6439</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.1678</v>
+        <v>-8.0032</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4511</v>
+        <v>-3.1626</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.7167</v>
+        <v>-4.8406</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3763</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7236</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5694</v>
+        <v>-0.2809</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1542</v>
+        <v>-0.2781</v>
       </c>
       <c r="V24" t="n">
         <v>-3.8009</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.771199999999997</v>
+        <v>-8.130200000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4828999999999999</v>
+        <v>0.4827999999999997</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.254000000000001</v>
+        <v>-8.613</v>
       </c>
       <c r="G25" t="n">
         <v>-8.938099999999999</v>
@@ -2377,13 +2377,13 @@
         <v>-5.9313</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6079000000000003</v>
+        <v>-0.6078999999999986</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8779</v>
+        <v>3.877899999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.486</v>
+        <v>-4.486000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-8.3302</v>
@@ -2404,13 +2404,13 @@
         <v>12.828</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8327</v>
+        <v>-1.1915</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8071</v>
+        <v>0.8070999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.6399</v>
+        <v>-1.9986</v>
       </c>
       <c r="V25" t="n">
         <v>3.832199999999999</v>
